--- a/data/trans_orig/IP24_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26790</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43527</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44779</t>
+          <t>44975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58690</t>
+          <t>58113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83266</t>
+          <t>81587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93745</t>
+          <t>94111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110482</t>
+          <t>110386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108298</t>
+          <t>108102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125935</t>
+          <t>125520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>207083</t>
+          <t>208762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231659</t>
+          <t>232236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45343</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64636</t>
+          <t>64733</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>59696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91072</t>
+          <t>90993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118754</t>
+          <t>118046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130527</t>
+          <t>130430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149820</t>
+          <t>150849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>152183</t>
+          <t>152446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171406</t>
+          <t>171907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288551</t>
+          <t>289259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>316233</t>
+          <t>316312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>24013</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39189</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21964</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>38336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>50432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72095</t>
+          <t>71989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97996</t>
+          <t>98482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112788</t>
+          <t>113172</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112023</t>
+          <t>111321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127693</t>
+          <t>127226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214747</t>
+          <t>214853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236360</t>
+          <t>236410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>41372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63276</t>
+          <t>63176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45450</t>
+          <t>44061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>64516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92580</t>
+          <t>90113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121501</t>
+          <t>121138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146039</t>
+          <t>146139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166765</t>
+          <t>167943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141960</t>
+          <t>141956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161022</t>
+          <t>162411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294286</t>
+          <t>294649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>323207</t>
+          <t>325674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189808</t>
+          <t>189953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151063</t>
+          <t>150375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188270</t>
+          <t>187450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>313924</t>
+          <t>314300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366474</t>
+          <t>366319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489127</t>
+          <t>488982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525438</t>
+          <t>524416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>533078</t>
+          <t>533898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>570285</t>
+          <t>570973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033809</t>
+          <t>1033964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1086359</t>
+          <t>1085983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18579</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34045</t>
+          <t>33397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>37463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59766</t>
+          <t>60202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103641</t>
+          <t>104289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119107</t>
+          <t>119724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120357</t>
+          <t>119692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135249</t>
+          <t>135221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230104</t>
+          <t>229668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252110</t>
+          <t>252407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -3023,47 +3023,47 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>36375</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>54956</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>35153</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54185</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35153</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>67859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93235</t>
+          <t>93137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151536</t>
+          <t>150765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>170568</t>
+          <t>169346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176771</t>
+          <t>177654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194716</t>
+          <t>195612</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334359</t>
+          <t>334457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359664</t>
+          <t>359735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38639</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>53626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75870</t>
+          <t>75359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112382</t>
+          <t>111198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127998</t>
+          <t>127968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127325</t>
+          <t>127591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143632</t>
+          <t>143495</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244446</t>
+          <t>244957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>268308</t>
+          <t>266690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31187</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>50141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38952</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57209</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85099</t>
+          <t>84444</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156972</t>
+          <t>157838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176792</t>
+          <t>177209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163982</t>
+          <t>163459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180105</t>
+          <t>179944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>325815</t>
+          <t>326470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353705</t>
+          <t>352772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>126031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101268</t>
+          <t>101381</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134647</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238919</t>
+          <t>237913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>285448</t>
+          <t>284186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544603</t>
+          <t>545706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>579403</t>
+          <t>579707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>608309</t>
+          <t>606500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>641688</t>
+          <t>641575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1163246</t>
+          <t>1164508</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1209775</t>
+          <t>1210781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23054</t>
+          <t>23164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63279</t>
+          <t>63414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93843</t>
+          <t>92956</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109966</t>
+          <t>109856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118958</t>
+          <t>117906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133111</t>
+          <t>132965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>216770</t>
+          <t>216635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239245</t>
+          <t>238418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35354</t>
+          <t>35689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53770</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,82 +4985,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>17,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>43336</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>34703</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>53989</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>15,51%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>24,13%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>87161</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>73512</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>100392</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>17,06%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>43336</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>34115</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>87161</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>74981</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>101418</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153477</t>
+          <t>153907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171893</t>
+          <t>171558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,82 +5098,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>82,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>180416</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>169763</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>189049</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>80,63%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>75,87%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>84,49%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>343838</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>330607</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>357487</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>76,71%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>82,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>180416</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>170119</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>189637</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,63%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>76,03%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>343838</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>329581</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>356018</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>79,78%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>76,47%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43263</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49181</t>
+          <t>48663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70334</t>
+          <t>70824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112734</t>
+          <t>114207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129298</t>
+          <t>129727</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132888</t>
+          <t>132512</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147195</t>
+          <t>146726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251636</t>
+          <t>251146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272789</t>
+          <t>273307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56508</t>
+          <t>56294</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>44557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67628</t>
+          <t>69008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95013</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150242</t>
+          <t>150456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170178</t>
+          <t>170215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159677</t>
+          <t>159242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177017</t>
+          <t>176266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315536</t>
+          <t>314738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342921</t>
+          <t>341541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171778</t>
+          <t>172716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109816</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142331</t>
+          <t>139898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255880</t>
+          <t>255509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>302504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>531236</t>
+          <t>530298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>566260</t>
+          <t>566322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>598222</t>
+          <t>600655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>630737</t>
+          <t>632549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1139444</t>
+          <t>1141063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1187687</t>
+          <t>1188058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23163</t>
+          <t>23781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56516</t>
+          <t>57988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73198</t>
+          <t>73915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93738</t>
+          <t>93120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104511</t>
+          <t>104917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83367</t>
+          <t>81895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123150</t>
+          <t>122897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183585</t>
+          <t>182868</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224002</t>
+          <t>223201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>28850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56017</t>
+          <t>55665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32880</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53565</t>
+          <t>52693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65177</t>
+          <t>68299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99670</t>
+          <t>101247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134495</t>
+          <t>134847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161708</t>
+          <t>161662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200142</t>
+          <t>201014</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220827</t>
+          <t>221937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344550</t>
+          <t>342973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>379043</t>
+          <t>375921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40797</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110048</t>
+          <t>118019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53479</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81804</t>
+          <t>81443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165109</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79537</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148788</t>
+          <t>148076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129389</t>
+          <t>129109</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151163</t>
+          <t>151884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207344</t>
+          <t>208891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>290649</t>
+          <t>291010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23014</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41758</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32404</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45030</t>
+          <t>44310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67622</t>
+          <t>68836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125073</t>
+          <t>125322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143817</t>
+          <t>144167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148834</t>
+          <t>147533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164592</t>
+          <t>163831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280447</t>
+          <t>279233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303039</t>
+          <t>303759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125608</t>
+          <t>124635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>237866</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>115769</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252371</t>
+          <t>251372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>368345</t>
+          <t>362673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425963</t>
+          <t>434516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538221</t>
+          <t>539194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>588444</t>
+          <t>589268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>641684</t>
+          <t>641928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1053181</t>
+          <t>1058853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1169155</t>
+          <t>1170154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP24_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35312</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27852</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45089</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>34556</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26886</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43161</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>27375</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>43447</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25,17%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>35312</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27557</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>44975</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58113</t>
+          <t>59139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81587</t>
+          <t>82595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>117765</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>107988</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125225</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102716</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>94111</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>110386</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>93825</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>109897</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>74,83%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>117765</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>108102</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>125520</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208762</t>
+          <t>207754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232236</t>
+          <t>231210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>137272</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>137272</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>137272</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>49692</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39781</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>59459</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54188</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44314</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>64733</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44828</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>64896</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>27,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>49692</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>40235</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>59696</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90993</t>
+          <t>90857</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118046</t>
+          <t>117014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>162450</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>152683</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>172361</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>81,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>140975</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>130430</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>150849</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>130267</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>150335</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,23%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>162450</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>152446</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>171907</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>76,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>289259</t>
+          <t>290291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>316312</t>
+          <t>316448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29577</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22446</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38197</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>31129</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24013</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38703</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>24598</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39235</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>22,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>29577</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>22431</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>38336</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50432</t>
+          <t>50237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71989</t>
+          <t>72038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>120080</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>111460</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127211</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>106056</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>98482</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>113172</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>97950</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>112587</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>77,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>120080</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>111321</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>127226</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,24%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214853</t>
+          <t>214804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236410</t>
+          <t>236605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137185</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137185</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137185</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54292</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44975</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>66377</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51857</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41372</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>63176</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41368</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>63018</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54292</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44061</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>64516</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90113</t>
+          <t>91222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121138</t>
+          <t>121459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>152180</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140095</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>161497</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>157458</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>146139</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167943</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>146297</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>167947</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>75,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>69,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>152180</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>141956</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>162411</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294649</t>
+          <t>294328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325674</t>
+          <t>324565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206472</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206472</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206472</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206472</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206472</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>151269</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>187574</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>171730</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>154519</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>189953</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>154794</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>190240</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>168873</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>150375</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>187450</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>314300</t>
+          <t>313929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366319</t>
+          <t>365840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>552475</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>533774</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>570079</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>755</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>507205</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>488982</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>524416</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>488695</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>524141</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>74,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>72,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>552475</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>533898</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>570973</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033964</t>
+          <t>1034443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1085983</t>
+          <t>1086354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>721348</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>721348</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>721348</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>678935</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>678935</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>678935</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>721348</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>721348</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>721348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23391</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16138</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31234</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24981</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17962</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33397</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18452</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33779</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23391</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16964</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32493</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37463</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60202</t>
+          <t>59256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>128794</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>120951</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>136047</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,63%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>112705</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>104289</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>119724</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>103907</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>119234</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>86,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>128794</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>119692</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>135221</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,63%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229668</t>
+          <t>230614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252407</t>
+          <t>251495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>152185</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>152185</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>152185</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>137686</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>137686</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>137686</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>152185</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>152185</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>152185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35153</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26812</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44321</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>44578</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36375</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54956</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35655</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>54742</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35153</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>26261</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>44219</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67859</t>
+          <t>67690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93137</t>
+          <t>93778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>186720</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>177552</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>195061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>161143</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>150765</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>169346</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>150979</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>170066</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>186720</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>177654</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>195612</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,16%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334457</t>
+          <t>333816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359735</t>
+          <t>359904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221873</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221873</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221873</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205721</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205721</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205721</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221873</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221873</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221873</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29737</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21390</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37734</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33802</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26384</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43154</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26260</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42930</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>29737</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>22469</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>38373</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,92%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>52419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75359</t>
+          <t>74116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>136227</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>128230</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>144574</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>120550</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>111198</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>127968</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>111422</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>128092</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>136227</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>127591</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>143495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>82,08%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244957</t>
+          <t>246200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>267897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165964</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165964</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165964</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154352</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154352</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154352</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165964</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165964</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30165</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22341</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38923</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>40090</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30770</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50141</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30505</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50519</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>30165</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22990</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>39475</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58142</t>
+          <t>58375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84444</t>
+          <t>83570</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172769</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>164011</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>180593</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167889</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157838</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>177209</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>157460</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>177474</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,72%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172769</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>163459</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>179944</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,14%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>326470</t>
+          <t>327344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>352772</t>
+          <t>352539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202934</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202934</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202934</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207979</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207979</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207979</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202934</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202934</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>102726</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>136006</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>143451</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>126031</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>160032</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>127592</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>161534</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>118446</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>101381</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>136456</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237913</t>
+          <t>235037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284186</t>
+          <t>285202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>624510</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>606950</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>640230</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>86,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>562287</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>545706</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>579707</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>544204</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>578146</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>77,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>624510</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>606500</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>641575</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1164508</t>
+          <t>1163492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1210781</t>
+          <t>1213657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>742956</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>742956</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>742956</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>705738</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>705738</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>705738</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>742956</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>742956</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>742956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20576</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13784</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28511</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>30965</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23164</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40064</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23709</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40694</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20576</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14064</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29123</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41631</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63414</t>
+          <t>62929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>126453</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>118518</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>133245</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102055</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>92956</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>109856</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>92326</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>109311</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>126453</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>117906</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>132965</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>216635</t>
+          <t>217120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238418</t>
+          <t>238705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147029</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147029</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147029</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133020</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133020</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133020</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147029</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147029</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147029</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43336</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35312</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53871</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>43826</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35689</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>53340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35212</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>53619</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>43336</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>34703</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>53989</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>74192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100392</t>
+          <t>99599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>180416</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>169881</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>188440</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>163421</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>153907</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>171558</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>153628</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>172035</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>180416</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>169763</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>189049</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330607</t>
+          <t>331400</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>357487</t>
+          <t>356807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223752</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223752</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223752</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223752</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223752</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223752</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25272</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18194</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33444</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33783</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26270</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41790</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26722</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41784</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,66%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25272</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19247</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33461</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48663</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70824</t>
+          <t>70229</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140701</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132529</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>147779</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122214</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>114207</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129727</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>114213</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>129275</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,34%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140701</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>132512</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146726</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,77%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251146</t>
+          <t>251741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273307</t>
+          <t>273230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165973</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165973</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165973</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165973</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165973</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165973</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35220</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27175</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45637</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>45792</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36535</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>56294</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36305</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>55642</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35220</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27533</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>44557</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69008</t>
+          <t>68411</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95811</t>
+          <t>95936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>168579</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158162</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>176624</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>160958</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>150456</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>170215</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>151108</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>170445</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>77,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>168579</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>159242</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>176266</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>82,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314738</t>
+          <t>314613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341541</t>
+          <t>342138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203799</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203799</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203799</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206750</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206750</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206750</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203799</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203799</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203799</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>107953</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140703</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>154366</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>136692</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>172716</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>137167</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>171263</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,96%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>124404</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>108004</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>139898</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255509</t>
+          <t>254577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302504</t>
+          <t>303220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>616149</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>599850</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>632600</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>822</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>548648</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>530298</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>566322</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>531751</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>565847</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>78,04%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>80,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>875</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>616149</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>600655</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>632549</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,2%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1141063</t>
+          <t>1140347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1188058</t>
+          <t>1188990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -6220,52 +6220,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>703014</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703014</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703014</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24438</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14630</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45206</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17241</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11984</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23781</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57988</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73915</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>101050</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80282</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>110858</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>63,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>99660</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>93120</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104917</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85,25%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>104748</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81895</t>
+          <t>98493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122897</t>
+          <t>109684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>210670</t>
+          <t>205798</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>181269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223201</t>
+          <t>216629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32536</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23939</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41649</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40049</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28850</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>55665</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41390</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>81439</t>
+          <t>63569</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68299</t>
+          <t>52589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101247</t>
+          <t>75791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>203385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>194272</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>211982</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>150463</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>134847</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>161662</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>78,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>212317</t>
+          <t>153380</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201014</t>
+          <t>144362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221937</t>
+          <t>160745</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>362781</t>
+          <t>356765</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>342973</t>
+          <t>344543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375921</t>
+          <t>367745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34957</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26161</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45846</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66418</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>41509</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>118019</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30984</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>46523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>107775</t>
+          <t>70957</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81443</t>
+          <t>58404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163562</t>
+          <t>86164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131486</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120597</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140282</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>123167</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71566</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>64,97%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>141511</t>
+          <t>120204</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129109</t>
+          <t>109681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151884</t>
+          <t>129133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>264678</t>
+          <t>251690</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208891</t>
+          <t>236483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291010</t>
+          <t>264243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23414</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31636</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31687</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22664</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41509</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>21724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>37514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>52470</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68836</t>
+          <t>63790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>145962</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137740</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>152225</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>135144</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>125322</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144167</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>81,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>157356</t>
+          <t>137103</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147533</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163831</t>
+          <t>144436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>292500</t>
+          <t>283066</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279233</t>
+          <t>271746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303759</t>
+          <t>293378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>98906</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144738</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>124635</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>229313</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>128550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251372</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362673</t>
+          <t>256861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>581884</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>552490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>598322</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>508434</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>434516</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>539194</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>622196</t>
+          <t>515435</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>589268</t>
+          <t>498972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>641928</t>
+          <t>530485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1130630</t>
+          <t>1097319</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058853</t>
+          <t>1067889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1170154</t>
+          <t>1120398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
